--- a/ai_logs/Nguyễn Hoài Nhi AI_Log/Nguyen_Hoai_Nhi.AI_AuditLog_Template.xlsx
+++ b/ai_logs/Nguyễn Hoài Nhi AI_Log/Nguyen_Hoai_Nhi.AI_AuditLog_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\LAB211 - Nhom-5\ai_logs\Nguyễn Hoài Nhi AI_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C168910A-F365-434A-8A4F-C01AB492B428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A04281F-57A3-4343-A2E2-25B445FA6856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="213">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -502,9 +502,6 @@
     <t>Kept Payroll Admin / Simulator User actor and refined responsibilities</t>
   </si>
   <si>
-    <t>Entry 001 — Project Structure</t>
-  </si>
-  <si>
     <t>Project Architecture</t>
   </si>
   <si>
@@ -523,9 +520,6 @@
     <t>Chat history</t>
   </si>
   <si>
-    <t>Entry 002 — Class Responsibility</t>
-  </si>
-  <si>
     <t>LEARNING</t>
   </si>
   <si>
@@ -541,9 +535,6 @@
     <t>Explained responsibilities of entities, repositories, controllers, and views</t>
   </si>
   <si>
-    <t>Entry 003 — Entity Understanding</t>
-  </si>
-  <si>
     <t>Model Layer</t>
   </si>
   <si>
@@ -557,27 +548,6 @@
   </si>
   <si>
     <t>Helped me understand relationship between Java objects and CSV files</t>
-  </si>
-  <si>
-    <t>Entry 004 — SalaryCalculator</t>
-  </si>
-  <si>
-    <t>Entry 005 — Optimistic Locking</t>
-  </si>
-  <si>
-    <t>Entry 006 — Flowchart Design</t>
-  </si>
-  <si>
-    <t>Entry 007 — DataGenerator Understanding</t>
-  </si>
-  <si>
-    <t>Entry 010 — Mermaid Diagram Correction</t>
-  </si>
-  <si>
-    <t>Entry 009 — Use Case Review</t>
-  </si>
-  <si>
-    <t>Entry 008 — NetBeans Setup</t>
   </si>
   <si>
     <t>SalaryCalculator</t>
@@ -1573,255 +1543,263 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>156</v>
+      <c r="A7" s="7">
+        <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="H7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>175</v>
+      <c r="A10" s="7">
+        <v>4</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>176</v>
+      <c r="A11" s="7">
+        <v>5</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="7" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="H13" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>8</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>180</v>
+      <c r="A15" s="7">
+        <v>9</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>10</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>221</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
